--- a/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 004.xlsx
+++ b/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 004.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Powerchina\Tecnopilotes\Registros de Calidad\04 AG-07 (19-12-25)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E345B0-41F2-46B9-9804-E22480CD0826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5036D1D1-4A09-4CDF-8CD8-8B023DE55557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -959,6 +959,138 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
@@ -988,138 +1120,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1729,167 +1729,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="65" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="74" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="75"/>
+      <c r="O1" s="76"/>
     </row>
     <row r="2" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="77"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="78"/>
     </row>
     <row r="3" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A3" s="47"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="77"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="78"/>
     </row>
     <row r="4" spans="1:20" ht="35.25" customHeight="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="82"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="41"/>
     </row>
     <row r="5" spans="1:20" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="59" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="62" t="s">
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="63"/>
-      <c r="O5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="65"/>
     </row>
     <row r="6" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="86"/>
-      <c r="E6" s="57" t="s">
+      <c r="D6" s="45"/>
+      <c r="E6" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="57" t="s">
+      <c r="J6" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="57" t="s">
+      <c r="K6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="57" t="s">
+      <c r="L6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="57" t="s">
+      <c r="M6" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="57" t="s">
+      <c r="N6" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="57" t="s">
+      <c r="O6" s="35" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="36.75" customHeight="1" thickBot="1">
-      <c r="A7" s="58"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
       <c r="Q7" s="2" t="s">
         <v>45</v>
       </c>
@@ -1910,10 +1910,10 @@
       <c r="B8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="80"/>
       <c r="E8" s="16" t="s">
         <v>17</v>
       </c>
@@ -1974,10 +1974,10 @@
       <c r="B9" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="16" t="s">
         <v>17</v>
       </c>
@@ -2022,10 +2022,10 @@
       <c r="B10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="80"/>
       <c r="E10" s="16" t="s">
         <v>17</v>
       </c>
@@ -2070,10 +2070,10 @@
       <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="80"/>
       <c r="E11" s="16" t="s">
         <v>17</v>
       </c>
@@ -2118,10 +2118,10 @@
       <c r="B12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="80"/>
       <c r="E12" s="16" t="s">
         <v>17</v>
       </c>
@@ -2178,10 +2178,10 @@
       <c r="B13" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="38"/>
+      <c r="D13" s="82"/>
       <c r="E13" s="23" t="s">
         <v>17</v>
       </c>
@@ -2242,10 +2242,10 @@
       <c r="B14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="38"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="23" t="s">
         <v>17</v>
       </c>
@@ -2290,10 +2290,10 @@
       <c r="B15" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="38"/>
+      <c r="D15" s="82"/>
       <c r="E15" s="23" t="s">
         <v>17</v>
       </c>
@@ -2338,10 +2338,10 @@
       <c r="B16" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="38"/>
+      <c r="D16" s="82"/>
       <c r="E16" s="23" t="s">
         <v>17</v>
       </c>
@@ -2386,10 +2386,10 @@
       <c r="B17" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="38"/>
+      <c r="D17" s="82"/>
       <c r="E17" s="23" t="s">
         <v>17</v>
       </c>
@@ -2446,10 +2446,10 @@
       <c r="B18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="80"/>
       <c r="E18" s="16" t="s">
         <v>44</v>
       </c>
@@ -2510,10 +2510,10 @@
       <c r="B19" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="80"/>
       <c r="E19" s="16" t="s">
         <v>44</v>
       </c>
@@ -2558,10 +2558,10 @@
       <c r="B20" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="36"/>
+      <c r="D20" s="80"/>
       <c r="E20" s="16" t="s">
         <v>44</v>
       </c>
@@ -2606,10 +2606,10 @@
       <c r="B21" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="36"/>
+      <c r="D21" s="80"/>
       <c r="E21" s="16" t="s">
         <v>44</v>
       </c>
@@ -2654,10 +2654,10 @@
       <c r="B22" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="36"/>
+      <c r="D22" s="80"/>
       <c r="E22" s="16" t="s">
         <v>44</v>
       </c>
@@ -2698,8 +2698,8 @@
     <row r="23" spans="1:20" ht="39.75" customHeight="1" thickBot="1">
       <c r="A23" s="15"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
@@ -2713,61 +2713,61 @@
       <c r="O23" s="31"/>
     </row>
     <row r="24" spans="1:20" ht="39.75" customHeight="1">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="52"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="55"/>
     </row>
     <row r="25" spans="1:20" ht="30" customHeight="1" thickBot="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="56"/>
+      <c r="A25" s="56"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="59"/>
     </row>
     <row r="26" spans="1:20" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A26" s="42" t="s">
+      <c r="A26" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="39" t="s">
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="41"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="85"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
     </row>
@@ -2869,16 +2869,21 @@
     <filterColumn colId="12" showButton="0"/>
   </autoFilter>
   <mergeCells count="41">
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="A24:O25"/>
     <mergeCell ref="A6:A7"/>
@@ -2895,21 +2900,16 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="M6:M7"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
